--- a/Result/profitability/3088.xlsx
+++ b/Result/profitability/3088.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.86</v>
       </c>
       <c r="M2" t="n">
-        <v>1.53</v>
+        <v>1.50875</v>
       </c>
       <c r="N2" t="n">
-        <v>35.48375</v>
+        <v>34.94125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.71</v>
       </c>
       <c r="M3" t="n">
-        <v>1.34375</v>
+        <v>1.31625</v>
       </c>
       <c r="N3" t="n">
-        <v>35.6725</v>
+        <v>35.22875000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15375</v>
+        <v>1.2525</v>
       </c>
       <c r="N4" t="n">
-        <v>36.0425</v>
+        <v>35.78375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.055</v>
+        <v>1.345</v>
       </c>
       <c r="N5" t="n">
-        <v>36.3375</v>
+        <v>35.94</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.74</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18375</v>
+        <v>1.21125</v>
       </c>
       <c r="N6" t="n">
-        <v>36.785</v>
+        <v>36.6075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.97625</v>
+        <v>0.99</v>
       </c>
       <c r="N7" t="n">
-        <v>37.1775</v>
+        <v>37.04</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.76875</v>
+        <v>0.74125</v>
       </c>
       <c r="N8" t="n">
-        <v>37.51</v>
+        <v>37.29125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2493</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E75" t="n">
+        <v>805</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>294</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>301</v>
+      </c>
+      <c r="K75" t="n">
+        <v>222</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.67625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.45625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2200000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.09777777777777785</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05142521304731118</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08967851099830793</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
